--- a/tools/importer/reports/import-reservation-form.report.xlsx
+++ b/tools/importer/reports/import-reservation-form.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="61">
   <si>
     <t>_reportFile</t>
   </si>
@@ -40,18 +40,60 @@
     <t>url</t>
   </si>
   <si>
+    <t>variant</t>
+  </si>
+  <si>
+    <t>confirmation-all-set.report.json</t>
+  </si>
+  <si>
+    <t>["confirmation"]</t>
+  </si>
+  <si>
+    <t>confirmation-all-set</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>confirmation</t>
+  </si>
+  <si>
+    <t>2026-10-21T10:18:12.218Z</t>
+  </si>
+  <si>
+    <t>You're all set | JSW Motors</t>
+  </si>
+  <si>
+    <t>http://localhost:3000/drafts/confirmation/source-variant-b.html</t>
+  </si>
+  <si>
+    <t>variant-b</t>
+  </si>
+  <si>
+    <t>confirmation.report.json</t>
+  </si>
+  <si>
+    <t>2026-10-21T10:18:07.139Z</t>
+  </si>
+  <si>
+    <t>Reserved | JSW Motors</t>
+  </si>
+  <si>
+    <t>http://localhost:3000/drafts/confirmation/source-variant-a.html</t>
+  </si>
+  <si>
+    <t>variant-a</t>
+  </si>
+  <si>
     <t>footer.report.json</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>footer</t>
   </si>
   <si>
-    <t>success</t>
-  </si>
-  <si>
     <t>2026-10-06T12:00:28.457Z</t>
   </si>
   <si>
@@ -127,7 +169,7 @@
     <t>reservation-form</t>
   </si>
   <si>
-    <t>2026-10-21T07:30:33.912Z</t>
+    <t>2026-10-21T11:32:42.234Z</t>
   </si>
   <si>
     <t>Reserve Now | JSW Motors</t>
@@ -540,19 +582,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
     <col min="7" max="7" width="26" customWidth="1"/>
     <col min="8" max="9" width="50" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -580,212 +623,300 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s">
         <v>11</v>
       </c>
-      <c r="D2">
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4">
         <v>5</v>
       </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="E4" t="s">
         <v>14</v>
       </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" t="s">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" t="s">
         <v>14</v>
       </c>
+      <c r="F5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J5" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" t="s">
-        <v>25</v>
-      </c>
-      <c r="I4" t="s">
-        <v>26</v>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" t="s">
+        <v>39</v>
+      </c>
+      <c r="I6" t="s">
+        <v>40</v>
+      </c>
+      <c r="J6" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5">
-        <v>6</v>
-      </c>
-      <c r="E5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G6" t="s">
-        <v>32</v>
-      </c>
-      <c r="H6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
         <v>37</v>
       </c>
-      <c r="D7" t="s">
-        <v>10</v>
+      <c r="D7">
+        <v>6</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" t="s">
         <v>37</v>
       </c>
-      <c r="G7" t="s">
-        <v>38</v>
-      </c>
-      <c r="H7" t="s">
-        <v>39</v>
-      </c>
       <c r="I7" t="s">
-        <v>40</v>
+        <v>28</v>
+      </c>
+      <c r="J7" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I8" t="s">
-        <v>46</v>
+        <v>48</v>
+      </c>
+      <c r="J8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9" t="s">
+        <v>52</v>
+      </c>
+      <c r="H9" t="s">
+        <v>53</v>
+      </c>
+      <c r="I9" t="s">
+        <v>54</v>
+      </c>
+      <c r="J9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" t="s">
+        <v>57</v>
+      </c>
+      <c r="G10" t="s">
+        <v>58</v>
+      </c>
+      <c r="H10" t="s">
+        <v>59</v>
+      </c>
+      <c r="I10" t="s">
+        <v>60</v>
+      </c>
+      <c r="J10" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1"/>
+  <autoFilter ref="A1:J1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/tools/importer/reports/import-reservation-form.report.xlsx
+++ b/tools/importer/reports/import-reservation-form.report.xlsx
@@ -169,7 +169,7 @@
     <t>reservation-form</t>
   </si>
   <si>
-    <t>2026-10-21T11:32:42.234Z</t>
+    <t>2026-10-22T07:07:29.330Z</t>
   </si>
   <si>
     <t>Reserve Now | JSW Motors</t>

--- a/tools/importer/reports/import-reservation-form.report.xlsx
+++ b/tools/importer/reports/import-reservation-form.report.xlsx
@@ -169,7 +169,7 @@
     <t>reservation-form</t>
   </si>
   <si>
-    <t>2026-10-22T07:07:29.330Z</t>
+    <t>2026-10-23T10:26:17.068Z</t>
   </si>
   <si>
     <t>Reserve Now | JSW Motors</t>
